--- a/data/trans_bre/IP1002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,55</t>
+          <t>-2,96; 1,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,64</t>
+          <t>-5,32; 0,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,53</t>
+          <t>0,43; 6,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,8</t>
+          <t>-4,15; 2,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 0,53</t>
+          <t>-5,29; 0,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,0</t>
+          <t>-4,21; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -0,01</t>
+          <t>-9,31; -0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,95</t>
+          <t>-1,41; 3,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,09</t>
+          <t>-3,16; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,0</t>
+          <t>-4,73; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 0,0</t>
+          <t>-13,73; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,9</t>
+          <t>-3,06; 1,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,58</t>
+          <t>-4,97; 0,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,62</t>
+          <t>-0,88; 2,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,17</t>
+          <t>-1,82; 2,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,41; 182,39</t>
+          <t>-90,73; 167,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 35,94</t>
+          <t>-81,62; 32,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,3; 611,67</t>
+          <t>-55,84; 753,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,69</t>
+          <t>-0,53; 5,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,33</t>
+          <t>-0,91; 4,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,43</t>
+          <t>-2,47; 2,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,32</t>
+          <t>-1,19; 4,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,0</t>
+          <t>-5,05; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,0</t>
+          <t>-5,92; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,87</t>
+          <t>-3,7; 1,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,14</t>
+          <t>-5,04; 1,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,21</t>
+          <t>-0,76; 1,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,36</t>
+          <t>-1,95; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,78</t>
+          <t>-1,15; 0,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,01</t>
+          <t>-1,16; 1,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 197,13</t>
+          <t>-52,57; 163,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,77; 24,72</t>
+          <t>-66,18; 29,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-60,72; 107,61</t>
+          <t>-63,97; 90,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 136,04</t>
+          <t>-60,79; 150,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,52</t>
+          <t>-2,38; 1,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,65</t>
+          <t>-5,42; 0,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,0</t>
+          <t>0,26; 5,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,32</t>
+          <t>-3,79; 2,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 0,53</t>
+          <t>-5,81; 0,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,0</t>
+          <t>-4,0; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -0,0</t>
+          <t>-9,77; -0,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,95</t>
+          <t>-1,41; 4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,92</t>
+          <t>-3,0; 3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,0</t>
+          <t>-4,18; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 0,0</t>
+          <t>-11,11; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,03</t>
+          <t>-3,07; 1,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,56</t>
+          <t>-5,17; 0,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,67</t>
+          <t>-1,0; 2,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,29</t>
+          <t>-1,71; 2,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,73; 167,18</t>
+          <t>-88,83; 228,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,62; 32,35</t>
+          <t>-82,53; 37,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 753,29</t>
+          <t>-66,99; 707,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,34</t>
+          <t>-0,06; 5,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,12</t>
+          <t>-0,91; 4,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,83</t>
+          <t>-2,46; 2,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,16</t>
+          <t>-1,36; 3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 0,0</t>
+          <t>-5,49; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,0</t>
+          <t>-7,3; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,9</t>
+          <t>-2,94; 1,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,14</t>
+          <t>-4,89; 1,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,12</t>
+          <t>-0,75; 1,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,41</t>
+          <t>-2,05; 0,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,81</t>
+          <t>-1,1; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,07</t>
+          <t>-1,31; 0,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,57; 163,72</t>
+          <t>-51,3; 189,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 29,73</t>
+          <t>-65,5; 29,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-63,97; 90,26</t>
+          <t>-61,56; 83,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 150,09</t>
+          <t>-64,97; 119,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>800,49%</t>
+          <t>1010,22%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,52</t>
+          <t>-2,57; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,59</t>
+          <t>-4,16; 0,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,5</t>
+          <t>0,54; 7,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-3,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-87,52%</t>
+          <t>-89,89%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,34</t>
+          <t>-3,72; 2,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,55</t>
+          <t>-5,15; 0,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,0</t>
+          <t>-3,83; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -0,46</t>
+          <t>-9,28; -0,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,0</t>
+          <t>-1,42; 3,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 3,17</t>
+          <t>-2,52; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,0</t>
+          <t>-4,25; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 0,0</t>
+          <t>-8,51; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,14</t>
+          <t>-2,93; 0,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,69</t>
+          <t>-4,95; 0,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,75</t>
+          <t>-1,14; 2,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,18</t>
+          <t>-1,64; 2,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,83; 228,97</t>
+          <t>-88,41; 182,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 37,5</t>
+          <t>-84,7; 35,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 707,19</t>
+          <t>-67,3; 611,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,76</t>
+          <t>-0,03; 5,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,33</t>
+          <t>-0,9; 4,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,65</t>
+          <t>-2,13; 2,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,78</t>
+          <t>-1,29; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-52,62%</t>
+          <t>-63,18%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,0</t>
+          <t>-4,04; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,0</t>
+          <t>-6,18; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,89</t>
+          <t>-2,96; 1,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 1,13</t>
+          <t>-5,19; 0,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-7,09%</t>
+          <t>-3,12%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,2</t>
+          <t>-0,79; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,48</t>
+          <t>-1,98; 0,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,75</t>
+          <t>-1,15; 0,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,94</t>
+          <t>-1,33; 1,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 189,35</t>
+          <t>-50,24; 197,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-65,5; 29,79</t>
+          <t>-64,77; 24,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 83,04</t>
+          <t>-60,72; 107,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-64,97; 119,06</t>
+          <t>-63,71; 141,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,169 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-68,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1010,22%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.275950723086291</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.02526400205024515</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.376423683770714</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.459278546354411</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.03226805150449397</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.6809639222008138</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>10.1022066268332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,45</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 1,55</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 0,64</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 7,19</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.569657701482162</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.158756177580644</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.5371913064243483</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.446142442583547</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.547284236707107</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6449331236099981</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.193507250485255</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,38</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-13,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-72,46%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-89,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,72; 2,8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 0,53</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,28; -0,24</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.2422886471287394</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.611181138097996</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.229661261474888</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.37597191887561</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1375319024141759</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.7246223789466948</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.8989415476974389</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.724958628598008</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.14500713379003</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.833332719303725</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.282194661706402</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 3,95</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 3,09</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,25; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,51; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.801918119278366</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5337074466972396</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.2441888768456231</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +789,181 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-42,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-46,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.293844219895564</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.03108179484765661</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.8285489356624715</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.761023185004835</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.416088193338346</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.0204590383321273</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,93; 0,9</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,95; 0,58</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,14; 2,62</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,64; 2,8</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-88,41; 182,39</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-84,7; 35,94</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-67,3; 611,67</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.421120616588152</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.517702178239203</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.249321019485161</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.507966983748645</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.951868289342689</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.085374206783432</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>342,35%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>144,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,03; 5,69</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 4,33</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,13; 2,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,29; 3,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.8770570951645457</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.006459029237563</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8220474053887761</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.4921697831177517</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4247023360125658</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4687148752388233</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.6932479625031802</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.3843352356099147</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-1,79</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-3,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-63,18%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.932720442641039</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.954013346253307</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.138799640983375</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.63668917557366</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8840873245872055</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8470343702552268</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6729695555277971</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 0,0</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-6,18; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 1,87</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-5,19; 0,97</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.89929736355562</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5757171869322368</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.62219903145307</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.803846781435696</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.823873601955035</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3594337871139398</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>6.116660492690695</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +971,265 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-31,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-12,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-3,12%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>1.952740201074187</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.409179183856827</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.0683959259624464</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.5314787101138823</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>3.423511327731287</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1.444868954281625</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.04584104329533991</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.4714370565017271</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 1,21</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,98; 0,36</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; 0,78</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 1,12</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-50,24; 197,13</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-64,77; 24,72</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-60,72; 107,61</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-63,71; 141,74</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.02621027914636513</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.8987570627361177</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.132172454686579</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.287105961692522</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.693045580063417</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.332466588954341</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.427870634829484</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.87450522966187</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.003456863443397</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.790345676882414</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-0.0340494163462924</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-0.8298400718245537</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.03555846428125994</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.6317825387715913</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.036732861918186</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-6.177563491712084</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-2.95704375922733</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-5.192728455055629</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1.870379357523264</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.9692258646615659</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.1608465039255874</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.7223110854757766</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.1634012242900473</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.04480866626103506</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1404265137533548</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.3112000687806962</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.124524414465956</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.03123642204344044</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7935459973294661</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.975761191548152</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.151413219137506</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.329545306646835</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.5023906374620174</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.6476941870522195</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.6071966037216879</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.6371031545714281</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.206435097666042</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.358605165358876</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.783447796265932</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.12271504737026</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1.971333278626944</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.2472088403577955</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1.076142879523887</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1.41743290135379</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1237,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
